--- a/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
+++ b/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
@@ -1,35 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet name="3.1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="3.3" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="3.4.1" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="3.4.2" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="3.4.3" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="3.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="3.3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3.4.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.4.2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3.4.3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Protokoll" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">Versuch 3.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr.</t>
+    <t>Nr.</t>
   </si>
   <si>
     <t xml:space="preserve">Winkel 0,5°</t>
@@ -41,7 +39,7 @@
     <t xml:space="preserve">winkel in ° genau</t>
   </si>
   <si>
-    <t xml:space="preserve">-Abw</t>
+    <t>-Abw</t>
   </si>
   <si>
     <t xml:space="preserve">+ Abw</t>
@@ -50,7 +48,7 @@
     <t xml:space="preserve">Abw. Schnitt</t>
   </si>
   <si>
-    <t xml:space="preserve">Korrektur</t>
+    <t>Korrektur</t>
   </si>
   <si>
     <t xml:space="preserve">Geschätzte Abweichung:  (')</t>
@@ -86,13 +84,16 @@
     <t xml:space="preserve">𝜑1 ges.</t>
   </si>
   <si>
+    <t xml:space="preserve">Mittelwert 𝜸</t>
+  </si>
+  <si>
     <t xml:space="preserve">nach Links</t>
   </si>
   <si>
     <t xml:space="preserve">Abw. Kopie:</t>
   </si>
   <si>
-    <t xml:space="preserve">Korr.</t>
+    <t>Korr.</t>
   </si>
   <si>
     <t xml:space="preserve">Negative abweichung von der kleineren zahl</t>
@@ -104,7 +105,7 @@
     <t xml:space="preserve">Postivite vaweichung von der größeren</t>
   </si>
   <si>
-    <t xml:space="preserve">Farbe</t>
+    <t>Farbe</t>
   </si>
   <si>
     <t xml:space="preserve"> λ in nm</t>
@@ -113,16 +114,16 @@
     <t xml:space="preserve">W (°)</t>
   </si>
   <si>
-    <t xml:space="preserve">W(')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W-Abw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W+Abw</t>
+    <t>W(')</t>
+  </si>
+  <si>
+    <t>Wges</t>
+  </si>
+  <si>
+    <t>W-Abw</t>
+  </si>
+  <si>
+    <t>W+Abw</t>
   </si>
   <si>
     <t xml:space="preserve">Schnitt M1 &amp; M2</t>
@@ -137,25 +138,25 @@
     <t xml:space="preserve">Schnitt Korrigiert</t>
   </si>
   <si>
-    <t xml:space="preserve">Dunkelrot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gelb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaugrün</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violett</t>
+    <t>Dunkelrot</t>
+  </si>
+  <si>
+    <t>Rot</t>
+  </si>
+  <si>
+    <t>Gelb</t>
+  </si>
+  <si>
+    <t>Grün</t>
+  </si>
+  <si>
+    <t>Blaugrün</t>
+  </si>
+  <si>
+    <t>Blau</t>
+  </si>
+  <si>
+    <t>Violett</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -189,51 +190,45 @@
   </si>
   <si>
     <t xml:space="preserve">Duchschnitt fehler in farben</t>
+  </si>
+  <si>
+    <t>λ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>min</t>
+    </r>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -245,137 +240,75 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF5B9BD5"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFED7D31"/>
-      <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FFA5A5A5"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -385,7 +318,6 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -397,17 +329,21 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Arial"/>
               </a:rPr>
               <a:t>Schnitt &amp; Abw.</a:t>
             </a:r>
+            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -421,10 +357,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0622593068035944"/>
-          <c:y val="0.0186021991263745"/>
-          <c:w val="0.921402730773719"/>
-          <c:h val="0.861726163578852"/>
+          <c:x val="0.062259"/>
+          <c:y val="0.018602"/>
+          <c:w val="0.921403"/>
+          <c:h val="0.861726"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -444,11 +380,14 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
               <a:srgbClr val="5B9BD5"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="5B9BD5"/>
               </a:solidFill>
@@ -459,39 +398,38 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:leaderLines>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="28440" cap="rnd">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:separator xml:space="preserve"> </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -568,11 +506,14 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
               <a:srgbClr val="ED7D31"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="ED7D31"/>
               </a:solidFill>
@@ -583,39 +524,38 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:leaderLines>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="28440" cap="rnd">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:separator xml:space="preserve"> </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -692,11 +632,14 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
               <a:srgbClr val="A5A5A5"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
@@ -707,39 +650,38 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:leaderLines>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="28440" cap="rnd">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:separator xml:space="preserve"> </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -802,14 +744,27 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:ln w="0">
               <a:noFill/>
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="44079618"/>
         <c:axId val="53467223"/>
       </c:lineChart>
@@ -824,7 +779,10 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="out"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:ln w="9360">
             <a:solidFill>
               <a:schemeClr val="dk1">
@@ -847,11 +805,11 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr/>
           </a:p>
         </c:txPr>
         <c:crossAx val="53467223"/>
@@ -865,13 +823,16 @@
         <c:axId val="53467223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="49.7"/>
-          <c:min val="46.7"/>
+          <c:max val="49.700000"/>
+          <c:min val="46.700000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:ln w="9360">
               <a:solidFill>
                 <a:schemeClr val="dk1">
@@ -887,7 +848,10 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:ln w="6480">
             <a:noFill/>
           </a:ln>
@@ -904,18 +868,21 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr/>
           </a:p>
         </c:txPr>
         <c:crossAx val="44079618"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -924,8 +891,12 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -943,18 +914,26 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0">
+      <a:off x="7804800" y="3149280"/>
+      <a:ext cx="6169320" cy="4779720"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
     <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
@@ -972,10 +951,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -985,7 +972,6 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -997,17 +983,21 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Arial"/>
               </a:rPr>
               <a:t>Schnitt &amp; Abw.</a:t>
             </a:r>
+            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -1021,10 +1011,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0622958469435371"/>
-          <c:y val="0.0185965968980575"/>
-          <c:w val="0.921371908539431"/>
-          <c:h val="0.861767806053305"/>
+          <c:x val="0.062296"/>
+          <c:y val="0.018597"/>
+          <c:w val="0.921372"/>
+          <c:h val="0.861768"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1044,11 +1034,14 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
               <a:srgbClr val="ED7D31"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="ED7D31"/>
               </a:solidFill>
@@ -1059,39 +1052,38 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:leaderLines>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="28440" cap="rnd">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:separator xml:space="preserve"> </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1168,11 +1160,14 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
               <a:srgbClr val="5B9BD5"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="5B9BD5"/>
               </a:solidFill>
@@ -1183,6 +1178,27 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:dLblPos val="r"/>
+            <c:leaderLines>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="28440" cap="rnd">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:separator xml:space="preserve">; </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1195,35 +1211,13 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                     <a:ea typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1300,11 +1294,14 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
               <a:srgbClr val="A5A5A5"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A5A5A5"/>
               </a:solidFill>
@@ -1315,6 +1312,27 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:dLblPos val="r"/>
+            <c:leaderLines>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="28440" cap="rnd">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:separator xml:space="preserve">; </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1327,35 +1345,13 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                     <a:ea typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1418,14 +1414,27 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:ln w="0">
               <a:noFill/>
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="72002339"/>
         <c:axId val="37973536"/>
       </c:lineChart>
@@ -1440,7 +1449,10 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="out"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:ln w="9360">
             <a:solidFill>
               <a:schemeClr val="dk1">
@@ -1463,11 +1475,11 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr/>
           </a:p>
         </c:txPr>
         <c:crossAx val="37973536"/>
@@ -1485,7 +1497,10 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
-          <c:spPr>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:ln w="9360">
               <a:solidFill>
                 <a:schemeClr val="dk1">
@@ -1501,7 +1516,10 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:ln w="6480">
             <a:noFill/>
           </a:ln>
@@ -1518,18 +1536,21 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr/>
           </a:p>
         </c:txPr>
         <c:crossAx val="72002339"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -1538,8 +1559,12 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -1557,18 +1582,26 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0">
+      <a:off x="7336080" y="3436920"/>
+      <a:ext cx="6171480" cy="4781160"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
     <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
@@ -1611,7 +1644,6 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -1620,9 +1652,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-      <a:uFillTx/>
-    </a:defRPr>
+    <cs:defRPr sz="1000" b="0" u="none" strike="noStrike"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1630,14 +1660,17 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
       <a:solidFill>
         <a:schemeClr val="bg1"/>
       </a:solidFill>
@@ -1665,9 +1698,12 @@
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
@@ -1691,12 +1727,6 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1823,6 +1853,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
   </cs:wall>
+  <cs:dataPointMarkerLayout/>
 </cs:chartStyle>
 </file>
 
@@ -1830,7 +1861,6 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -1839,9 +1869,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-      <a:uFillTx/>
-    </a:defRPr>
+    <cs:defRPr sz="1000" b="0" u="none" strike="noStrike"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1849,14 +1877,17 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
       <a:solidFill>
         <a:schemeClr val="bg1"/>
       </a:solidFill>
@@ -1884,9 +1915,12 @@
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
@@ -1910,12 +1944,6 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2042,11 +2070,12 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor"/>
   </cs:wall>
+  <cs:dataPointMarkerLayout/>
 </cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -2063,9 +2092,11 @@
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="1" name=""/>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="7804800" y="3149280"/>
         <a:ext cx="6169320" cy="4779720"/>
       </xdr:xfrm>
@@ -2081,7 +2112,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
@@ -2098,9 +2129,11 @@
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name=""/>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="7336080" y="3436920"/>
         <a:ext cx="6171480" cy="4781160"/>
       </xdr:xfrm>
@@ -2115,8 +2148,291 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -2158,17 +2474,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2195,7 +2511,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2219,7 +2534,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2279,31 +2593,31 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:O11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.15"/>
+    <col customWidth="1" min="4" max="4" style="0" width="13.15"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+    <row r="2" ht="14.25">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="14.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -2324,14 +2638,14 @@
       <c r="K5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="0" t="s">
+      <c r="O5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="14.25">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -2339,102 +2653,99 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+    <row r="7" ht="14.25">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="0" t="n">
+      <c r="D7">
         <v>359.5</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <f aca="false">D7+(E7/60)</f>
-        <v>359.533333333333</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <f aca="false">G7-(1/60)</f>
-        <v>359.516666666667</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <f aca="false">G7+(1/60)</f>
-        <v>359.55</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <f aca="false">AVERAGE(G7,G8)</f>
-        <v>359.525</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <f aca="false">M7-360</f>
-        <v>-0.475000000000023</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+      <c r="G7">
+        <f t="shared" ref="G7:G8" si="0">D7+(E7/60)</f>
+        <v>359.53333333333302</v>
+      </c>
+      <c r="I7">
+        <f t="shared" ref="I7:I8" si="1">G7-(1/60)</f>
+        <v>359.51666666666699</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ref="K7:K8" si="2">G7+(1/60)</f>
+        <v>359.55000000000001</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(G7,G8)</f>
+        <v>359.52499999999998</v>
+      </c>
+      <c r="O7">
+        <f>M7-360</f>
+        <v>-0.47500000000002301</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>359.5</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <f aca="false">D8+(E8/60)</f>
-        <v>359.516666666667</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <f aca="false">G8-(1/60)</f>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>359.51666666666699</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
         <v>359.5</v>
       </c>
-      <c r="K8" s="0" t="n">
-        <f aca="false">G8+(1/60)</f>
-        <v>359.533333333333</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>359.53333333333302</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70069444444444484" right="0.70069444444444484" top="0.75208333333333299" bottom="0.75208333333333299" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="C4:K16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+    <row r="4" ht="14.25">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">'3.1'!E11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L4">
+        <f>'3.1'!O7</f>
+        <v>-0.47500000000002301</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
@@ -2448,490 +2759,498 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="n">
+    <row r="8" ht="14.25">
+      <c r="C8">
         <v>253.5</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>4</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8">
         <v>313.5</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0" t="s">
+    <row r="12" ht="14.25">
+      <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="14.25">
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <f aca="false">C8+(D8/60)</f>
+      <c r="D14">
+        <f>C8+(D8/60)</f>
         <v>253.566666666667</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <f aca="false">D14-($K$4/60)</f>
-        <v>253.55</v>
-      </c>
-      <c r="H14" s="0" t="n">
-        <f aca="false">D14+($K$4/60)</f>
-        <v>253.583333333333</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14">
+        <f>D14+($L$4)</f>
+        <v>253.09166666666698</v>
+      </c>
+      <c r="H14">
+        <f>D14-($L$4)</f>
+        <v>254.04166666666703</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
       <c r="C15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="14.25">
       <c r="C16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="0" t="n">
-        <f aca="false">F8+(G8/60)</f>
-        <v>313.55</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <f aca="false">D16-($K$4/60)</f>
-        <v>313.533333333333</v>
-      </c>
-      <c r="H16" s="0" t="n">
-        <f aca="false">D16+($K$4/60)</f>
-        <v>313.566666666667</v>
+      <c r="D16">
+        <f>F8+(G8/60)</f>
+        <v>313.55000000000001</v>
+      </c>
+      <c r="F16">
+        <f>D16+($L$4)</f>
+        <v>313.07499999999999</v>
+      </c>
+      <c r="H16">
+        <f>D16-($L$4)</f>
+        <v>314.02500000000003</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="C22" s="3">
+        <f>(D14-D16)/2</f>
+        <v>-29.991666666666504</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70069444444444484" right="0.70069444444444484" top="0.75208333333333299" bottom="0.75208333333333299" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B3:U34"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.58"/>
+    <col customWidth="1" min="4" max="4" style="0" width="13.58"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="0" t="s">
+    <row r="3" ht="14.25">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="0" t="n">
-        <f aca="false">'3.1'!E11</f>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <f>'3.1'!E11</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <f aca="false">'3.1'!O7</f>
-        <v>-0.475000000000023</v>
-      </c>
-      <c r="Q4" s="0" t="s">
+    <row r="4" ht="14.25">
+      <c r="D4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="E4">
+        <f>'3.1'!O7</f>
+        <v>-0.47500000000002301</v>
+      </c>
+      <c r="Q4" t="s">
         <v>24</v>
       </c>
-      <c r="Q6" s="0" t="s">
+    </row>
+    <row r="6" ht="14.25">
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="Q6" t="s">
         <v>26</v>
       </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
       <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10">
+        <v>706.53999999999996</v>
+      </c>
+      <c r="F10">
+        <v>47</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <f t="shared" ref="H10:H29" si="3">F10+(G10/60)</f>
+        <v>47.016666666666701</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ref="J10:J29" si="4">H10-($E$3/60)</f>
+        <v>47</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ref="K10:K29" si="5">H10+($E$3/60)</f>
+        <v>47.033333333333303</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ref="N10:N16" si="6">AVERAGE(H10,H23)</f>
+        <v>47.008333333333297</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q10:Q11" si="7">H23-($E$3/60)</f>
+        <v>46.983333333333299</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S10:S11" si="8">H10+($E$3/60)</f>
+        <v>47.033333333333303</v>
+      </c>
+      <c r="U10">
+        <f t="shared" ref="U10:U16" si="9">N10+$E$4</f>
+        <v>46.533333333333303</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>667.82000000000005</v>
+      </c>
+      <c r="F11">
+        <v>47</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="3"/>
+        <v>47.183333333333302</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="4"/>
+        <v>47.1666666666667</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="5"/>
+        <v>47.200000000000003</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="6"/>
+        <v>47.174999999999997</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="7"/>
+        <v>47.149999999999999</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>47.200000000000003</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="9"/>
+        <v>46.700000000000003</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12">
+        <v>587.55999999999995</v>
+      </c>
+      <c r="F12">
+        <v>47.5</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="3"/>
+        <v>47.700000000000003</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>47.683333333333302</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="5"/>
+        <v>47.716666666666697</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="6"/>
+        <v>47.725000000000001</v>
+      </c>
+      <c r="Q12">
+        <f>H12-($E$3/60)</f>
+        <v>47.683333333333302</v>
+      </c>
+      <c r="S12">
+        <f>H25+($E$3/60)</f>
+        <v>47.766666666666701</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="9"/>
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13">
+        <v>501.56999999999999</v>
+      </c>
+      <c r="F13">
+        <v>48.5</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>48.649999999999999</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>48.633333333333297</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>48.6666666666667</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="6"/>
+        <v>48.649999999999999</v>
+      </c>
+      <c r="Q13">
+        <f>N13-($E$3/60)</f>
+        <v>48.633333333333297</v>
+      </c>
+      <c r="S13">
+        <f>N13+($E$3/60)</f>
+        <v>48.6666666666667</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="9"/>
+        <v>48.174999999999997</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14">
+        <v>492.19</v>
+      </c>
+      <c r="F14">
+        <v>48.5</v>
+      </c>
+      <c r="G14">
+        <v>17</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>48.783333333333303</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="4"/>
+        <v>48.766666666666701</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="5"/>
+        <v>48.799999999999997</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="6"/>
+        <v>48.7916666666667</v>
+      </c>
+      <c r="Q14">
+        <f>H14-($E$3/60)</f>
+        <v>48.766666666666701</v>
+      </c>
+      <c r="S14">
+        <f>H27+($E$3/60)</f>
+        <v>48.816666666666698</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="9"/>
+        <v>48.316666666666599</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15">
+        <v>447.14999999999998</v>
+      </c>
+      <c r="F15">
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>49.116666666666703</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="4"/>
+        <v>49.100000000000001</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="5"/>
+        <v>49.133333333333297</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="6"/>
+        <v>49.108333333333299</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q15:Q16" si="10">H28-($E$3/60)</f>
+        <v>49.0833333333333</v>
+      </c>
+      <c r="S15">
+        <f t="shared" ref="S15:S16" si="11">H15+($E$3/60)</f>
+        <v>49.133333333333297</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="9"/>
+        <v>48.633333333333297</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16">
+        <v>438.79000000000002</v>
+      </c>
+      <c r="F16">
+        <v>49.5</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>49.616666666666703</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="4"/>
+        <v>49.600000000000001</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="5"/>
+        <v>49.633333333333297</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="6"/>
+        <v>49.600000000000001</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="10"/>
+        <v>49.566666666666698</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="11"/>
+        <v>49.633333333333297</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="9"/>
+        <v>49.125</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="O17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="E21" s="4"/>
+      <c r="F21" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="G21" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="H21" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="I21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="K21" t="s">
         <v>33</v>
       </c>
-      <c r="Q8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="U8" s="0" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>706.54</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>47</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <f aca="false">F10+(G10/60)</f>
-        <v>47.0166666666667</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <f aca="false">H10-($E$3/60)</f>
-        <v>47</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <f aca="false">H10+($E$3/60)</f>
-        <v>47.0333333333333</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <f aca="false">AVERAGE(H10,H23)</f>
-        <v>47.0083333333333</v>
-      </c>
-      <c r="Q10" s="0" t="n">
-        <f aca="false">H23-($E$3/60)</f>
-        <v>46.9833333333333</v>
-      </c>
-      <c r="S10" s="0" t="n">
-        <f aca="false">H10+($E$3/60)</f>
-        <v>47.0333333333333</v>
-      </c>
-      <c r="U10" s="0" t="n">
-        <f aca="false">N10+$E$4</f>
-        <v>46.5333333333333</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>667.82</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>47</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <f aca="false">F11+(G11/60)</f>
-        <v>47.1833333333333</v>
-      </c>
-      <c r="J11" s="0" t="n">
-        <f aca="false">H11-($E$3/60)</f>
-        <v>47.1666666666667</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <f aca="false">H11+($E$3/60)</f>
-        <v>47.2</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <f aca="false">AVERAGE(H11,H24)</f>
-        <v>47.175</v>
-      </c>
-      <c r="Q11" s="0" t="n">
-        <f aca="false">H24-($E$3/60)</f>
-        <v>47.15</v>
-      </c>
-      <c r="S11" s="0" t="n">
-        <f aca="false">H11+($E$3/60)</f>
-        <v>47.2</v>
-      </c>
-      <c r="U11" s="0" t="n">
-        <f aca="false">N11+$E$4</f>
-        <v>46.7</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>587.56</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" s="0" t="n">
-        <f aca="false">F12+(G12/60)</f>
-        <v>47.7</v>
-      </c>
-      <c r="J12" s="0" t="n">
-        <f aca="false">H12-($E$3/60)</f>
-        <v>47.6833333333333</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <f aca="false">H12+($E$3/60)</f>
-        <v>47.7166666666667</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <f aca="false">AVERAGE(H12,H25)</f>
-        <v>47.725</v>
-      </c>
-      <c r="Q12" s="0" t="n">
-        <f aca="false">H12-($E$3/60)</f>
-        <v>47.6833333333333</v>
-      </c>
-      <c r="S12" s="0" t="n">
-        <f aca="false">H25+($E$3/60)</f>
-        <v>47.7666666666667</v>
-      </c>
-      <c r="U12" s="0" t="n">
-        <f aca="false">N12+$E$4</f>
-        <v>47.25</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>501.57</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="H13" s="0" t="n">
-        <f aca="false">F13+(G13/60)</f>
-        <v>48.65</v>
-      </c>
-      <c r="J13" s="0" t="n">
-        <f aca="false">H13-($E$3/60)</f>
-        <v>48.6333333333333</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <f aca="false">H13+($E$3/60)</f>
-        <v>48.6666666666667</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <f aca="false">AVERAGE(H13,H26)</f>
-        <v>48.65</v>
-      </c>
-      <c r="Q13" s="0" t="n">
-        <f aca="false">N13-($E$3/60)</f>
-        <v>48.6333333333333</v>
-      </c>
-      <c r="S13" s="0" t="n">
-        <f aca="false">N13+($E$3/60)</f>
-        <v>48.6666666666667</v>
-      </c>
-      <c r="U13" s="0" t="n">
-        <f aca="false">N13+$E$4</f>
-        <v>48.175</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>492.19</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="H14" s="0" t="n">
-        <f aca="false">F14+(G14/60)</f>
-        <v>48.7833333333333</v>
-      </c>
-      <c r="J14" s="0" t="n">
-        <f aca="false">H14-($E$3/60)</f>
-        <v>48.7666666666667</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <f aca="false">H14+($E$3/60)</f>
-        <v>48.8</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <f aca="false">AVERAGE(H14,H27)</f>
-        <v>48.7916666666667</v>
-      </c>
-      <c r="Q14" s="0" t="n">
-        <f aca="false">H14-($E$3/60)</f>
-        <v>48.7666666666667</v>
-      </c>
-      <c r="S14" s="0" t="n">
-        <f aca="false">H27+($E$3/60)</f>
-        <v>48.8166666666667</v>
-      </c>
-      <c r="U14" s="0" t="n">
-        <f aca="false">N14+$E$4</f>
-        <v>48.3166666666666</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>447.15</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>49</v>
-      </c>
-      <c r="G15" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="0" t="n">
-        <f aca="false">F15+(G15/60)</f>
-        <v>49.1166666666667</v>
-      </c>
-      <c r="J15" s="0" t="n">
-        <f aca="false">H15-($E$3/60)</f>
-        <v>49.1</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <f aca="false">H15+($E$3/60)</f>
-        <v>49.1333333333333</v>
-      </c>
-      <c r="N15" s="0" t="n">
-        <f aca="false">AVERAGE(H15,H28)</f>
-        <v>49.1083333333333</v>
-      </c>
-      <c r="Q15" s="0" t="n">
-        <f aca="false">H28-($E$3/60)</f>
-        <v>49.0833333333333</v>
-      </c>
-      <c r="S15" s="0" t="n">
-        <f aca="false">H15+($E$3/60)</f>
-        <v>49.1333333333333</v>
-      </c>
-      <c r="U15" s="0" t="n">
-        <f aca="false">N15+$E$4</f>
-        <v>48.6333333333333</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>438.79</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="0" t="n">
-        <f aca="false">F16+(G16/60)</f>
-        <v>49.6166666666667</v>
-      </c>
-      <c r="J16" s="0" t="n">
-        <f aca="false">H16-($E$3/60)</f>
-        <v>49.6</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <f aca="false">H16+($E$3/60)</f>
-        <v>49.6333333333333</v>
-      </c>
-      <c r="N16" s="0" t="n">
-        <f aca="false">AVERAGE(H16,H29)</f>
-        <v>49.6</v>
-      </c>
-      <c r="Q16" s="0" t="n">
-        <f aca="false">H29-($E$3/60)</f>
-        <v>49.5666666666667</v>
-      </c>
-      <c r="S16" s="0" t="n">
-        <f aca="false">H16+($E$3/60)</f>
-        <v>49.6333333333333</v>
-      </c>
-      <c r="U16" s="0" t="n">
-        <f aca="false">N16+$E$4</f>
-        <v>49.125</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O17" s="0" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="0" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" ht="14.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -2943,249 +3262,246 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="str">
-        <f aca="false">B10</f>
+    <row r="23" ht="14.25">
+      <c r="B23" t="str">
+        <f t="shared" ref="B23:B29" si="12">B10</f>
         <v>Dunkelrot</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="4" t="n">
-        <v>706.54</v>
+      <c r="D23" s="4">
+        <v>706.53999999999996</v>
       </c>
       <c r="E23" s="4"/>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="4">
         <v>47</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="4">
         <v>0</v>
       </c>
-      <c r="H23" s="4" t="n">
-        <f aca="false">F23+(G23/60)</f>
+      <c r="H23" s="4">
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="4" t="n">
-        <f aca="false">H23-($E$3/60)</f>
-        <v>46.9833333333333</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <f aca="false">H23+($E$3/60)</f>
-        <v>47.0166666666667</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="str">
-        <f aca="false">B11</f>
+      <c r="J23" s="4">
+        <f t="shared" si="4"/>
+        <v>46.983333333333299</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="5"/>
+        <v>47.016666666666701</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="B24" t="str">
+        <f t="shared" si="12"/>
         <v>Rot</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="4" t="n">
-        <v>667.82</v>
+      <c r="D24" s="4">
+        <v>667.82000000000005</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="4">
         <v>47</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="4">
         <v>10</v>
       </c>
-      <c r="H24" s="4" t="n">
-        <f aca="false">F24+(G24/60)</f>
+      <c r="H24" s="4">
+        <f t="shared" si="3"/>
         <v>47.1666666666667</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="4" t="n">
-        <f aca="false">H24-($E$3/60)</f>
-        <v>47.15</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <f aca="false">H24+($E$3/60)</f>
-        <v>47.1833333333333</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="str">
-        <f aca="false">B12</f>
+      <c r="J24" s="4">
+        <f t="shared" si="4"/>
+        <v>47.149999999999999</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="5"/>
+        <v>47.183333333333302</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="B25" t="str">
+        <f t="shared" si="12"/>
         <v>Gelb</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="4" t="n">
-        <v>587.56</v>
+      <c r="D25" s="4">
+        <v>587.55999999999995</v>
       </c>
       <c r="E25" s="4"/>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="4">
         <v>47.5</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="4">
         <v>15</v>
       </c>
-      <c r="H25" s="4" t="n">
-        <f aca="false">F25+(G25/60)</f>
+      <c r="H25" s="4">
+        <f t="shared" si="3"/>
         <v>47.75</v>
       </c>
       <c r="I25" s="4"/>
-      <c r="J25" s="4" t="n">
-        <f aca="false">H25-($E$3/60)</f>
-        <v>47.7333333333333</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <f aca="false">H25+($E$3/60)</f>
-        <v>47.7666666666667</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="str">
-        <f aca="false">B13</f>
+      <c r="J25" s="4">
+        <f t="shared" si="4"/>
+        <v>47.733333333333299</v>
+      </c>
+      <c r="K25" s="4">
+        <f t="shared" si="5"/>
+        <v>47.766666666666701</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="B26" t="str">
+        <f t="shared" si="12"/>
         <v>Grün</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="4" t="n">
-        <v>501.57</v>
+      <c r="D26" s="4">
+        <v>501.56999999999999</v>
       </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="4">
         <v>48.5</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="4">
         <v>9</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <f aca="false">F26+(G26/60)</f>
-        <v>48.65</v>
+      <c r="H26" s="4">
+        <f t="shared" si="3"/>
+        <v>48.649999999999999</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="4" t="n">
-        <f aca="false">H26-($E$3/60)</f>
-        <v>48.6333333333333</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <f aca="false">H26+($E$3/60)</f>
+      <c r="J26" s="4">
+        <f t="shared" si="4"/>
+        <v>48.633333333333297</v>
+      </c>
+      <c r="K26" s="4">
+        <f t="shared" si="5"/>
         <v>48.6666666666667</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="str">
-        <f aca="false">B14</f>
+    <row r="27" ht="14.25">
+      <c r="B27" t="str">
+        <f t="shared" si="12"/>
         <v>Blaugrün</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>492.19</v>
       </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="4">
         <v>48.5</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="4">
         <v>18</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <f aca="false">F27+(G27/60)</f>
-        <v>48.8</v>
+      <c r="H27" s="4">
+        <f t="shared" si="3"/>
+        <v>48.799999999999997</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="4" t="n">
-        <f aca="false">H27-($E$3/60)</f>
-        <v>48.7833333333333</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <f aca="false">H27+($E$3/60)</f>
-        <v>48.8166666666667</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="str">
-        <f aca="false">B15</f>
+      <c r="J27" s="4">
+        <f t="shared" si="4"/>
+        <v>48.783333333333303</v>
+      </c>
+      <c r="K27" s="4">
+        <f t="shared" si="5"/>
+        <v>48.816666666666698</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="B28" t="str">
+        <f t="shared" si="12"/>
         <v>Blau</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="4" t="n">
-        <v>447.15</v>
+      <c r="D28" s="4">
+        <v>447.14999999999998</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="4">
         <v>49</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="4">
         <v>6</v>
       </c>
-      <c r="H28" s="4" t="n">
-        <f aca="false">F28+(G28/60)</f>
-        <v>49.1</v>
+      <c r="H28" s="4">
+        <f t="shared" si="3"/>
+        <v>49.100000000000001</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="4" t="n">
-        <f aca="false">H28-($E$3/60)</f>
+      <c r="J28" s="4">
+        <f t="shared" si="4"/>
         <v>49.0833333333333</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <f aca="false">H28+($E$3/60)</f>
-        <v>49.1166666666667</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="str">
-        <f aca="false">B16</f>
+      <c r="K28" s="4">
+        <f t="shared" si="5"/>
+        <v>49.116666666666703</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="B29" t="str">
+        <f t="shared" si="12"/>
         <v>Violett</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="4" t="n">
-        <v>438.79</v>
+      <c r="D29" s="4">
+        <v>438.79000000000002</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="4">
         <v>49.5</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="4">
         <v>5</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <f aca="false">F29+(G29/60)</f>
+      <c r="H29" s="4">
+        <f t="shared" si="3"/>
         <v>49.5833333333333</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="4" t="n">
-        <f aca="false">H29-($E$3/60)</f>
-        <v>49.5666666666667</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <f aca="false">H29+($E$3/60)</f>
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J29" s="4">
+        <f t="shared" si="4"/>
+        <v>49.566666666666698</v>
+      </c>
+      <c r="K29" s="4">
+        <f t="shared" si="5"/>
+        <v>49.600000000000001</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
       <c r="H34" s="4"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70069444444444484" right="0.70069444444444484" top="0.75208333333333299" bottom="0.75208333333333299" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B3:W46"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="14.25">
       <c r="B3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <f aca="false">'3.1'!E11</f>
+        <v>22</v>
+      </c>
+      <c r="E3" s="4">
+        <f>'3.1'!E11</f>
         <v>1</v>
       </c>
       <c r="F3" s="4"/>
@@ -3207,15 +3523,15 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="14.25">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <f aca="false">'3.1'!O7</f>
-        <v>-0.475000000000023</v>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4">
+        <f>'3.1'!O7</f>
+        <v>-0.47500000000002301</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -3228,8 +3544,8 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="0" t="s">
-        <v>23</v>
+      <c r="Q4" t="s">
+        <v>24</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -3238,7 +3554,7 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="14.25">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3262,9 +3578,9 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="14.25">
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3280,8 +3596,8 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
-      <c r="Q6" s="0" t="s">
-        <v>25</v>
+      <c r="Q6" t="s">
+        <v>26</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -3290,7 +3606,7 @@
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="14.25">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -3314,53 +3630,53 @@
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="14.25">
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="0" t="s">
-        <v>27</v>
+      <c r="D8" t="s">
+        <v>28</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="0" t="s">
-        <v>34</v>
+      <c r="Q8" t="s">
+        <v>35</v>
       </c>
       <c r="R8" s="4"/>
-      <c r="S8" s="0" t="s">
-        <v>35</v>
+      <c r="S8" t="s">
+        <v>36</v>
       </c>
       <c r="T8" s="4"/>
-      <c r="U8" s="0" t="s">
-        <v>36</v>
+      <c r="U8" t="s">
+        <v>37</v>
       </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="14.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -3384,385 +3700,385 @@
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="14.25">
       <c r="B10" s="4" t="str">
-        <f aca="false">'3.4.1'!B10</f>
+        <f>'3.4.1'!B10</f>
         <v>Dunkelrot</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="4" t="n">
-        <v>706.54</v>
+      <c r="D10" s="4">
+        <v>706.53999999999996</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>312</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4">
         <v>22</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <f aca="false">F10+(G10/60)</f>
-        <v>312.366666666667</v>
+      <c r="H10" s="4">
+        <f t="shared" ref="H10:H29" si="13">F10+(G10/60)</f>
+        <v>312.36666666666702</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="4" t="n">
-        <f aca="false">H10-($E$3/60)</f>
-        <v>312.35</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <f aca="false">H10+($E$3/60)</f>
-        <v>312.383333333333</v>
+      <c r="J10" s="4">
+        <f t="shared" ref="J10:J29" si="14">H10-($E$3/60)</f>
+        <v>312.35000000000002</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" ref="K10:K29" si="15">H10+($E$3/60)</f>
+        <v>312.38333333333298</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="4" t="n">
-        <f aca="false">AVERAGE(H10,H23)</f>
-        <v>312.35</v>
+      <c r="N10" s="4">
+        <f t="shared" ref="N10:N16" si="16">AVERAGE(H10,H23)</f>
+        <v>312.35000000000002</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4" t="n">
-        <f aca="false">H23-($E$3/60)</f>
+      <c r="Q10" s="4">
+        <f t="shared" ref="Q10:Q11" si="17">H23-($E$3/60)</f>
         <v>312.316666666667</v>
       </c>
       <c r="R10" s="4"/>
-      <c r="S10" s="4" t="n">
-        <f aca="false">H10+($E$3/60)</f>
-        <v>312.383333333333</v>
+      <c r="S10" s="4">
+        <f t="shared" ref="S10:S11" si="18">H10+($E$3/60)</f>
+        <v>312.38333333333298</v>
       </c>
       <c r="T10" s="4"/>
-      <c r="U10" s="4" t="n">
-        <f aca="false">N10-$E$4</f>
-        <v>312.825</v>
+      <c r="U10" s="4">
+        <f t="shared" ref="U10:U16" si="19">N10-$E$4</f>
+        <v>312.82499999999999</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="14.25">
       <c r="B11" s="4" t="str">
-        <f aca="false">'3.4.1'!B11</f>
+        <f>'3.4.1'!B11</f>
         <v>Rot</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="4" t="n">
-        <v>667.82</v>
+      <c r="D11" s="4">
+        <v>667.82000000000005</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>312</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4">
         <v>9</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <f aca="false">F11+(G11/60)</f>
-        <v>312.15</v>
+      <c r="H11" s="4">
+        <f t="shared" si="13"/>
+        <v>312.14999999999998</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="4" t="n">
-        <f aca="false">H11-($E$3/60)</f>
-        <v>312.133333333333</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <f aca="false">H11+($E$3/60)</f>
-        <v>312.166666666667</v>
+      <c r="J11" s="4">
+        <f t="shared" si="14"/>
+        <v>312.13333333333298</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="15"/>
+        <v>312.16666666666703</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="4" t="n">
-        <f aca="false">AVERAGE(H11,H24)</f>
-        <v>312.15</v>
+      <c r="N11" s="4">
+        <f t="shared" si="16"/>
+        <v>312.14999999999998</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
-      <c r="Q11" s="4" t="n">
-        <f aca="false">H24-($E$3/60)</f>
-        <v>312.133333333333</v>
+      <c r="Q11" s="4">
+        <f t="shared" si="17"/>
+        <v>312.13333333333298</v>
       </c>
       <c r="R11" s="4"/>
-      <c r="S11" s="4" t="n">
-        <f aca="false">H11+($E$3/60)</f>
-        <v>312.166666666667</v>
+      <c r="S11" s="4">
+        <f t="shared" si="18"/>
+        <v>312.16666666666703</v>
       </c>
       <c r="T11" s="4"/>
-      <c r="U11" s="4" t="n">
-        <f aca="false">N11-$E$4</f>
+      <c r="U11" s="4">
+        <f t="shared" si="19"/>
         <v>312.625</v>
       </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="14.25">
       <c r="B12" s="4" t="str">
-        <f aca="false">'3.4.1'!B12</f>
+        <f>'3.4.1'!B12</f>
         <v>Gelb</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4" t="n">
-        <v>587.56</v>
+      <c r="D12" s="4">
+        <v>587.55999999999995</v>
       </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="4">
         <v>311.5</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="4">
         <v>6</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <f aca="false">F12+(G12/60)</f>
-        <v>311.6</v>
+      <c r="H12" s="4">
+        <f t="shared" si="13"/>
+        <v>311.60000000000002</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="4" t="n">
-        <f aca="false">H12-($E$3/60)</f>
-        <v>311.583333333333</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <f aca="false">H12+($E$3/60)</f>
-        <v>311.616666666667</v>
+      <c r="J12" s="4">
+        <f t="shared" si="14"/>
+        <v>311.58333333333297</v>
+      </c>
+      <c r="K12" s="4">
+        <f t="shared" si="15"/>
+        <v>311.61666666666702</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="4" t="n">
-        <f aca="false">AVERAGE(H12,H25)</f>
-        <v>311.6</v>
+      <c r="N12" s="4">
+        <f t="shared" si="16"/>
+        <v>311.60000000000002</v>
       </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
-      <c r="Q12" s="4" t="n">
-        <f aca="false">H12-($E$3/60)</f>
-        <v>311.583333333333</v>
+      <c r="Q12" s="4">
+        <f t="shared" ref="Q12:Q16" si="20">H12-($E$3/60)</f>
+        <v>311.58333333333297</v>
       </c>
       <c r="R12" s="4"/>
-      <c r="S12" s="4" t="n">
-        <f aca="false">H25+($E$3/60)</f>
-        <v>311.616666666667</v>
+      <c r="S12" s="4">
+        <f>H25+($E$3/60)</f>
+        <v>311.61666666666702</v>
       </c>
       <c r="T12" s="4"/>
-      <c r="U12" s="4" t="n">
-        <f aca="false">N12-$E$4</f>
-        <v>312.075</v>
+      <c r="U12" s="4">
+        <f t="shared" si="19"/>
+        <v>312.07499999999999</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="14.25">
       <c r="B13" s="4" t="str">
-        <f aca="false">'3.4.1'!B13</f>
+        <f>'3.4.1'!B13</f>
         <v>Grün</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="4" t="n">
-        <v>501.57</v>
+      <c r="D13" s="4">
+        <v>501.56999999999999</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="4">
         <v>310.5</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="4">
         <v>10</v>
       </c>
-      <c r="H13" s="4" t="n">
-        <f aca="false">F13+(G13/60)</f>
-        <v>310.666666666667</v>
+      <c r="H13" s="4">
+        <f t="shared" si="13"/>
+        <v>310.66666666666703</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="4" t="n">
-        <f aca="false">H13-($E$3/60)</f>
-        <v>310.65</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <f aca="false">H13+($E$3/60)</f>
+      <c r="J13" s="4">
+        <f t="shared" si="14"/>
+        <v>310.64999999999998</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="15"/>
         <v>310.683333333333</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="4" t="n">
-        <f aca="false">AVERAGE(H13,H26)</f>
-        <v>310.666666666667</v>
+      <c r="N13" s="4">
+        <f t="shared" si="16"/>
+        <v>310.66666666666703</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="4" t="n">
-        <f aca="false">H13-($E$3/60)</f>
-        <v>310.65</v>
+      <c r="Q13" s="4">
+        <f t="shared" si="20"/>
+        <v>310.64999999999998</v>
       </c>
       <c r="R13" s="4"/>
-      <c r="S13" s="4" t="n">
-        <f aca="false">N13+($E$3/60)</f>
+      <c r="S13" s="4">
+        <f>N13+($E$3/60)</f>
         <v>310.683333333333</v>
       </c>
       <c r="T13" s="4"/>
-      <c r="U13" s="4" t="n">
-        <f aca="false">N13-$E$4</f>
-        <v>311.141666666667</v>
+      <c r="U13" s="4">
+        <f t="shared" si="19"/>
+        <v>311.14166666666699</v>
       </c>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="14.25">
       <c r="B14" s="4" t="str">
-        <f aca="false">'3.4.1'!B14</f>
+        <f>'3.4.1'!B14</f>
         <v>Blaugrün</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>492.19</v>
       </c>
       <c r="E14" s="4"/>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="4">
         <v>310.5</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4">
         <v>1</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <f aca="false">F14+(G14/60)</f>
-        <v>310.516666666667</v>
+      <c r="H14" s="4">
+        <f t="shared" si="13"/>
+        <v>310.51666666666699</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="4" t="n">
-        <f aca="false">H14-($E$3/60)</f>
+      <c r="J14" s="4">
+        <f t="shared" si="14"/>
         <v>310.5</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <f aca="false">H14+($E$3/60)</f>
-        <v>310.533333333333</v>
+      <c r="K14" s="4">
+        <f t="shared" si="15"/>
+        <v>310.53333333333302</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="4" t="n">
-        <f aca="false">AVERAGE(H14,H27)</f>
-        <v>310.525</v>
+      <c r="N14" s="4">
+        <f t="shared" si="16"/>
+        <v>310.52499999999998</v>
       </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="4" t="n">
-        <f aca="false">H14-($E$3/60)</f>
+      <c r="Q14" s="4">
+        <f t="shared" si="20"/>
         <v>310.5</v>
       </c>
       <c r="R14" s="4"/>
-      <c r="S14" s="4" t="n">
-        <f aca="false">H27+($E$3/60)</f>
-        <v>310.55</v>
+      <c r="S14" s="4">
+        <f t="shared" ref="S14:S16" si="21">H27+($E$3/60)</f>
+        <v>310.55000000000001</v>
       </c>
       <c r="T14" s="4"/>
-      <c r="U14" s="4" t="n">
-        <f aca="false">N14-$E$4</f>
+      <c r="U14" s="4">
+        <f t="shared" si="19"/>
         <v>311</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="14.25">
       <c r="B15" s="4" t="str">
-        <f aca="false">'3.4.1'!B15</f>
+        <f>'3.4.1'!B15</f>
         <v>Blau</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="4" t="n">
-        <v>447.15</v>
+      <c r="D15" s="4">
+        <v>447.14999999999998</v>
       </c>
       <c r="E15" s="4"/>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="4">
         <v>310</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="4">
         <v>10</v>
       </c>
-      <c r="H15" s="4" t="n">
-        <f aca="false">F15+(G15/60)</f>
-        <v>310.166666666667</v>
+      <c r="H15" s="4">
+        <f t="shared" si="13"/>
+        <v>310.16666666666703</v>
       </c>
       <c r="I15" s="4"/>
-      <c r="J15" s="4" t="n">
-        <f aca="false">H15-($E$3/60)</f>
-        <v>310.15</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <f aca="false">H15+($E$3/60)</f>
+      <c r="J15" s="4">
+        <f t="shared" si="14"/>
+        <v>310.14999999999998</v>
+      </c>
+      <c r="K15" s="4">
+        <f t="shared" si="15"/>
         <v>310.183333333333</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="4" t="n">
-        <f aca="false">AVERAGE(H15,H28)</f>
-        <v>310.166666666667</v>
+      <c r="N15" s="4">
+        <f t="shared" si="16"/>
+        <v>310.16666666666703</v>
       </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="4" t="n">
-        <f aca="false">H15-($E$3/60)</f>
-        <v>310.15</v>
+      <c r="Q15" s="4">
+        <f t="shared" si="20"/>
+        <v>310.14999999999998</v>
       </c>
       <c r="R15" s="4"/>
-      <c r="S15" s="4" t="n">
-        <f aca="false">H28+($E$3/60)</f>
+      <c r="S15" s="4">
+        <f t="shared" si="21"/>
         <v>310.183333333333</v>
       </c>
       <c r="T15" s="4"/>
-      <c r="U15" s="4" t="n">
-        <f aca="false">N15-$E$4</f>
-        <v>310.641666666667</v>
+      <c r="U15" s="4">
+        <f t="shared" si="19"/>
+        <v>310.64166666666699</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="14.25">
       <c r="B16" s="4" t="str">
-        <f aca="false">'3.4.1'!B16</f>
+        <f>'3.4.1'!B16</f>
         <v>Violett</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="4" t="n">
-        <v>438.79</v>
+      <c r="D16" s="4">
+        <v>438.79000000000002</v>
       </c>
       <c r="E16" s="4"/>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="4">
         <v>309.5</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="4">
         <v>10</v>
       </c>
-      <c r="H16" s="4" t="n">
-        <f aca="false">F16+(G16/60)</f>
-        <v>309.666666666667</v>
+      <c r="H16" s="4">
+        <f t="shared" si="13"/>
+        <v>309.66666666666703</v>
       </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="4" t="n">
-        <f aca="false">H16-($E$3/60)</f>
-        <v>309.65</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <f aca="false">H16+($E$3/60)</f>
+      <c r="J16" s="4">
+        <f t="shared" si="14"/>
+        <v>309.64999999999998</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="15"/>
         <v>309.683333333333</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="4" t="n">
-        <f aca="false">AVERAGE(H16,H29)</f>
-        <v>309.666666666667</v>
+      <c r="N16" s="4">
+        <f t="shared" si="16"/>
+        <v>309.66666666666703</v>
       </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="4" t="n">
-        <f aca="false">H16-($E$3/60)</f>
-        <v>309.65</v>
+      <c r="Q16" s="4">
+        <f t="shared" si="20"/>
+        <v>309.64999999999998</v>
       </c>
       <c r="R16" s="4"/>
-      <c r="S16" s="4" t="n">
-        <f aca="false">H29+($E$3/60)</f>
+      <c r="S16" s="4">
+        <f t="shared" si="21"/>
         <v>309.683333333333</v>
       </c>
       <c r="T16" s="4"/>
-      <c r="U16" s="4" t="n">
-        <f aca="false">N16-$E$4</f>
-        <v>310.141666666667</v>
+      <c r="U16" s="4">
+        <f t="shared" si="19"/>
+        <v>310.14166666666699</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="14.25">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -3777,7 +4093,7 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -3788,7 +4104,7 @@
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="14.25">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -3812,9 +4128,9 @@
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="14.25">
       <c r="B19" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -3838,7 +4154,7 @@
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="14.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -3862,32 +4178,32 @@
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="14.25">
       <c r="B21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -3902,7 +4218,7 @@
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="14.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -3926,34 +4242,34 @@
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="14.25">
       <c r="B23" s="4" t="str">
-        <f aca="false">B10</f>
+        <f t="shared" ref="B23:B29" si="22">B10</f>
         <v>Dunkelrot</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="4" t="n">
-        <v>706.54</v>
+      <c r="D23" s="4">
+        <v>706.53999999999996</v>
       </c>
       <c r="E23" s="4"/>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="4">
         <v>312</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="4">
         <v>20</v>
       </c>
-      <c r="H23" s="4" t="n">
-        <f aca="false">F23+(G23/60)</f>
-        <v>312.333333333333</v>
+      <c r="H23" s="4">
+        <f t="shared" si="13"/>
+        <v>312.33333333333297</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="4" t="n">
-        <f aca="false">H23-($E$3/60)</f>
+      <c r="J23" s="4">
+        <f t="shared" si="14"/>
         <v>312.316666666667</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <f aca="false">H23+($E$3/60)</f>
-        <v>312.35</v>
+      <c r="K23" s="4">
+        <f t="shared" si="15"/>
+        <v>312.35000000000002</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -3968,34 +4284,34 @@
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="14.25">
       <c r="B24" s="4" t="str">
-        <f aca="false">B11</f>
+        <f t="shared" si="22"/>
         <v>Rot</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="4" t="n">
-        <v>667.82</v>
+      <c r="D24" s="4">
+        <v>667.82000000000005</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="4">
         <v>312</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="4">
         <v>9</v>
       </c>
-      <c r="H24" s="4" t="n">
-        <f aca="false">F24+(G24/60)</f>
-        <v>312.15</v>
+      <c r="H24" s="4">
+        <f t="shared" si="13"/>
+        <v>312.14999999999998</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="4" t="n">
-        <f aca="false">H24-($E$3/60)</f>
-        <v>312.133333333333</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <f aca="false">H24+($E$3/60)</f>
-        <v>312.166666666667</v>
+      <c r="J24" s="4">
+        <f t="shared" si="14"/>
+        <v>312.13333333333298</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="15"/>
+        <v>312.16666666666703</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -4010,34 +4326,34 @@
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="14.25">
       <c r="B25" s="4" t="str">
-        <f aca="false">B12</f>
+        <f t="shared" si="22"/>
         <v>Gelb</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="4" t="n">
-        <v>587.56</v>
+      <c r="D25" s="4">
+        <v>587.55999999999995</v>
       </c>
       <c r="E25" s="4"/>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="4">
         <v>311.5</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="4">
         <v>6</v>
       </c>
-      <c r="H25" s="4" t="n">
-        <f aca="false">F25+(G25/60)</f>
-        <v>311.6</v>
+      <c r="H25" s="4">
+        <f t="shared" si="13"/>
+        <v>311.60000000000002</v>
       </c>
       <c r="I25" s="4"/>
-      <c r="J25" s="4" t="n">
-        <f aca="false">H25-($E$3/60)</f>
-        <v>311.583333333333</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <f aca="false">H25+($E$3/60)</f>
-        <v>311.616666666667</v>
+      <c r="J25" s="4">
+        <f t="shared" si="14"/>
+        <v>311.58333333333297</v>
+      </c>
+      <c r="K25" s="4">
+        <f t="shared" si="15"/>
+        <v>311.61666666666702</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -4052,33 +4368,33 @@
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="14.25">
       <c r="B26" s="4" t="str">
-        <f aca="false">B13</f>
+        <f t="shared" si="22"/>
         <v>Grün</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="4" t="n">
-        <v>501.57</v>
+      <c r="D26" s="4">
+        <v>501.56999999999999</v>
       </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="4">
         <v>310.5</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="4">
         <v>10</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <f aca="false">F26+(G26/60)</f>
-        <v>310.666666666667</v>
+      <c r="H26" s="4">
+        <f t="shared" si="13"/>
+        <v>310.66666666666703</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="4" t="n">
-        <f aca="false">H26-($E$3/60)</f>
-        <v>310.65</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <f aca="false">H26+($E$3/60)</f>
+      <c r="J26" s="4">
+        <f t="shared" si="14"/>
+        <v>310.64999999999998</v>
+      </c>
+      <c r="K26" s="4">
+        <f t="shared" si="15"/>
         <v>310.683333333333</v>
       </c>
       <c r="L26" s="4"/>
@@ -4094,34 +4410,34 @@
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="14.25">
       <c r="B27" s="4" t="str">
-        <f aca="false">B14</f>
+        <f t="shared" si="22"/>
         <v>Blaugrün</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>492.19</v>
       </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="4">
         <v>310.5</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="4">
         <v>2</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <f aca="false">F27+(G27/60)</f>
-        <v>310.533333333333</v>
+      <c r="H27" s="4">
+        <f t="shared" si="13"/>
+        <v>310.53333333333302</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="4" t="n">
-        <f aca="false">H27-($E$3/60)</f>
-        <v>310.516666666667</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <f aca="false">H27+($E$3/60)</f>
-        <v>310.55</v>
+      <c r="J27" s="4">
+        <f t="shared" si="14"/>
+        <v>310.51666666666699</v>
+      </c>
+      <c r="K27" s="4">
+        <f t="shared" si="15"/>
+        <v>310.55000000000001</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -4136,33 +4452,33 @@
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="14.25">
       <c r="B28" s="4" t="str">
-        <f aca="false">B15</f>
+        <f t="shared" si="22"/>
         <v>Blau</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="4" t="n">
-        <v>447.15</v>
+      <c r="D28" s="4">
+        <v>447.14999999999998</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="4">
         <v>310</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="4">
         <v>10</v>
       </c>
-      <c r="H28" s="4" t="n">
-        <f aca="false">F28+(G28/60)</f>
-        <v>310.166666666667</v>
+      <c r="H28" s="4">
+        <f t="shared" si="13"/>
+        <v>310.16666666666703</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="4" t="n">
-        <f aca="false">H28-($E$3/60)</f>
-        <v>310.15</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <f aca="false">H28+($E$3/60)</f>
+      <c r="J28" s="4">
+        <f t="shared" si="14"/>
+        <v>310.14999999999998</v>
+      </c>
+      <c r="K28" s="4">
+        <f t="shared" si="15"/>
         <v>310.183333333333</v>
       </c>
       <c r="L28" s="4"/>
@@ -4178,33 +4494,33 @@
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="14.25">
       <c r="B29" s="4" t="str">
-        <f aca="false">B16</f>
+        <f t="shared" si="22"/>
         <v>Violett</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="4" t="n">
-        <v>438.79</v>
+      <c r="D29" s="4">
+        <v>438.79000000000002</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="4">
         <v>309.5</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="4">
         <v>10</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <f aca="false">F29+(G29/60)</f>
-        <v>309.666666666667</v>
+      <c r="H29" s="4">
+        <f t="shared" si="13"/>
+        <v>309.66666666666703</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="4" t="n">
-        <f aca="false">H29-($E$3/60)</f>
-        <v>309.65</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <f aca="false">H29+($E$3/60)</f>
+      <c r="J29" s="4">
+        <f t="shared" si="14"/>
+        <v>309.64999999999998</v>
+      </c>
+      <c r="K29" s="4">
+        <f t="shared" si="15"/>
         <v>309.683333333333</v>
       </c>
       <c r="L29" s="4"/>
@@ -4220,7 +4536,7 @@
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="14.25">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -4244,7 +4560,7 @@
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="14.25">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -4268,7 +4584,7 @@
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="14.25">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -4292,7 +4608,7 @@
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="14.25">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -4316,7 +4632,7 @@
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="14.25">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -4340,7 +4656,7 @@
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="14.25">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -4364,7 +4680,7 @@
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="14.25">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -4388,7 +4704,7 @@
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="14.25">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -4412,7 +4728,7 @@
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="14.25">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -4436,7 +4752,7 @@
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="14.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -4460,7 +4776,7 @@
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="14.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -4484,7 +4800,7 @@
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="14.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -4508,7 +4824,7 @@
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="14.25">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -4532,7 +4848,7 @@
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="14.25">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -4556,7 +4872,7 @@
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="14.25">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -4580,7 +4896,7 @@
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="14.25">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -4604,7 +4920,7 @@
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="14.25">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -4629,325 +4945,449 @@
       <c r="W46" s="4"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70069444444444484" right="0.70069444444444484" top="0.75208333333333299" bottom="0.75208333333333299" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B4:M30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <sheetData>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="0" t="s">
+    <row r="4" ht="15">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="F4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="str">
-        <f aca="false">'3.4.1'!B10</f>
+      <c r="M4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" ht="15">
+      <c r="B7" t="str">
+        <f>'3.4.1'!B10</f>
         <v>Dunkelrot</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <f aca="false">'3.4.1'!N10</f>
-        <v>47.0083333333333</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <f aca="false" t="array" ref="F7:F13">'3.4.2'!N10:N16</f>
-        <v>312.35</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <f aca="false">D7-(360-F7)</f>
-        <v>-0.641666666666644</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="str">
-        <f aca="false">'3.4.1'!B11</f>
+      <c r="D7">
+        <f>'3.4.1'!N10</f>
+        <v>47.008333333333297</v>
+      </c>
+      <c r="F7">
+        <f t="array" ref="F7:F13">'3.4.2'!N10:N16</f>
+        <v>312.35000000000002</v>
+      </c>
+      <c r="M7">
+        <f t="shared" ref="M7:M9" si="23">D7-(360-F7)</f>
+        <v>-0.64166666666667993</v>
+      </c>
+    </row>
+    <row r="8" ht="15">
+      <c r="B8" t="str">
+        <f>'3.4.1'!B11</f>
         <v>Rot</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <f aca="false">'3.4.1'!N11</f>
-        <v>47.175</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>312.15</v>
-      </c>
-      <c r="M8" s="0" t="n">
-        <f aca="false">D8-(360-F8)</f>
-        <v>-0.675000000000026</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="str">
-        <f aca="false">'3.4.1'!B12</f>
+      <c r="D8">
+        <f>'3.4.1'!N11</f>
+        <v>47.174999999999997</v>
+      </c>
+      <c r="F8">
+        <f/>
+        <v>312.14999999999998</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="23"/>
+        <v>-0.67500000000002558</v>
+      </c>
+    </row>
+    <row r="9" ht="15">
+      <c r="B9" t="str">
+        <f>'3.4.1'!B12</f>
         <v>Gelb</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <f aca="false">'3.4.1'!N12</f>
-        <v>47.725</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <f aca="false">D9-(360-F9)</f>
-        <v>-0.674999999999976</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="str">
-        <f aca="false">'3.4.1'!B13</f>
+      <c r="D9">
+        <f>'3.4.1'!N12</f>
+        <v>47.725000000000001</v>
+      </c>
+      <c r="F9">
+        <f/>
+        <v>311.60000000000002</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="23"/>
+        <v>-0.67499999999997584</v>
+      </c>
+    </row>
+    <row r="10" ht="15">
+      <c r="B10" t="str">
+        <f>'3.4.1'!B13</f>
         <v>Grün</v>
       </c>
-      <c r="D10" s="0" t="n">
-        <f aca="false">'3.4.1'!N13</f>
-        <v>48.65</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>310.666666666667</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <f aca="false">D10-(360-F10)</f>
-        <v>-0.683333333333316</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="str">
-        <f aca="false">'3.4.1'!B14</f>
+      <c r="D10">
+        <f>'3.4.1'!N13</f>
+        <v>48.649999999999999</v>
+      </c>
+      <c r="F10">
+        <f/>
+        <v>310.66666666666703</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ref="M10:M13" si="24">D10-(360-F10)</f>
+        <v>-0.68333333333297475</v>
+      </c>
+    </row>
+    <row r="11" ht="15">
+      <c r="B11" t="str">
+        <f>'3.4.1'!B14</f>
         <v>Blaugrün</v>
       </c>
-      <c r="D11" s="0" t="n">
-        <f aca="false">'3.4.1'!N14</f>
+      <c r="D11">
+        <f>'3.4.1'!N14</f>
         <v>48.7916666666667</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>310.525</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <f aca="false">D11-(360-F11)</f>
-        <v>-0.683333333333358</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="str">
-        <f aca="false">'3.4.1'!B15</f>
+      <c r="F11">
+        <f/>
+        <v>310.52499999999998</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="24"/>
+        <v>-0.68333333333332291</v>
+      </c>
+    </row>
+    <row r="12" ht="15">
+      <c r="B12" t="str">
+        <f>'3.4.1'!B15</f>
         <v>Blau</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <f aca="false">'3.4.1'!N15</f>
-        <v>49.1083333333333</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>310.166666666667</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <f aca="false">D12-(360-F12)</f>
-        <v>-0.72499999999998</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="str">
-        <f aca="false">'3.4.1'!B16</f>
+      <c r="D12">
+        <f>'3.4.1'!N15</f>
+        <v>49.108333333333299</v>
+      </c>
+      <c r="F12">
+        <f/>
+        <v>310.16666666666703</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="24"/>
+        <v>-0.72499999999967457</v>
+      </c>
+    </row>
+    <row r="13" ht="15">
+      <c r="B13" t="str">
+        <f>'3.4.1'!B16</f>
         <v>Violett</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <f aca="false">'3.4.1'!N16</f>
-        <v>49.6</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>309.666666666667</v>
-      </c>
-      <c r="M13" s="0" t="n">
-        <f aca="false">D13-(360-F13)</f>
-        <v>-0.733333333333313</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13">
+        <f>'3.4.1'!N16</f>
+        <v>49.600000000000001</v>
+      </c>
+      <c r="F13">
+        <f/>
+        <v>309.66666666666703</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="24"/>
+        <v>-0.7333333333329719</v>
+      </c>
+    </row>
+    <row r="17" ht="15">
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="I17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" ht="15">
       <c r="B19" s="4" t="str">
-        <f aca="false">B7</f>
+        <f t="shared" ref="B19:B21" si="25">B7</f>
         <v>Dunkelrot</v>
       </c>
-      <c r="D19" s="0" t="n">
-        <f aca="false">'3.4.1'!U10</f>
-        <v>46.5333333333333</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <f aca="false">'3.4.2'!U10</f>
-        <v>312.825</v>
-      </c>
-      <c r="I19" s="0" t="n">
-        <f aca="false">D19-(360-F19)</f>
-        <v>-0.641666666666644</v>
-      </c>
-      <c r="L19" s="0" t="n">
-        <f aca="false">AVERAGE(I19:I25)</f>
-        <v>-0.68809523809523</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19">
+        <f>'3.4.1'!U10</f>
+        <v>46.533333333333303</v>
+      </c>
+      <c r="F19">
+        <f>'3.4.2'!U10</f>
+        <v>312.82499999999999</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ref="I19:I25" si="26">D19-(360-F19)</f>
+        <v>-0.64166666666670835</v>
+      </c>
+      <c r="L19">
+        <f>AVERAGE(I19:I25)</f>
+        <v>-0.68809523809512085</v>
+      </c>
+    </row>
+    <row r="20" ht="15">
       <c r="B20" s="4" t="str">
-        <f aca="false">B8</f>
+        <f t="shared" si="25"/>
         <v>Rot</v>
       </c>
-      <c r="D20" s="0" t="n">
-        <f aca="false">'3.4.1'!U11</f>
-        <v>46.7</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <f aca="false">'3.4.2'!U11</f>
+      <c r="D20">
+        <f>'3.4.1'!U11</f>
+        <v>46.700000000000003</v>
+      </c>
+      <c r="F20">
+        <f>'3.4.2'!U11</f>
         <v>312.625</v>
       </c>
-      <c r="I20" s="0" t="n">
-        <f aca="false">D20-(360-F20)</f>
-        <v>-0.675000000000026</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20">
+        <f t="shared" si="26"/>
+        <v>-0.67499999999999716</v>
+      </c>
+    </row>
+    <row r="21" ht="15">
       <c r="B21" s="4" t="str">
-        <f aca="false">B9</f>
+        <f t="shared" si="25"/>
         <v>Gelb</v>
       </c>
-      <c r="D21" s="0" t="n">
-        <f aca="false">'3.4.1'!U12</f>
+      <c r="D21">
+        <f>'3.4.1'!U12</f>
         <v>47.25</v>
       </c>
-      <c r="F21" s="0" t="n">
-        <f aca="false">'3.4.2'!U12</f>
-        <v>312.075</v>
-      </c>
-      <c r="I21" s="0" t="n">
-        <f aca="false">D21-(360-F21)</f>
-        <v>-0.674999999999976</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21">
+        <f>'3.4.2'!U12</f>
+        <v>312.07499999999999</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="26"/>
+        <v>-0.67500000000001137</v>
+      </c>
+    </row>
+    <row r="22" ht="15">
       <c r="B22" s="4" t="str">
-        <f aca="false">B10</f>
+        <f t="shared" ref="B22:B25" si="27">B10</f>
         <v>Grün</v>
       </c>
-      <c r="D22" s="0" t="n">
-        <f aca="false">'3.4.1'!U13</f>
-        <v>48.175</v>
-      </c>
-      <c r="F22" s="0" t="n">
-        <f aca="false">'3.4.2'!U13</f>
-        <v>311.141666666667</v>
-      </c>
-      <c r="I22" s="0" t="n">
-        <f aca="false">D22-(360-F22)</f>
-        <v>-0.683333333333316</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22">
+        <f>'3.4.1'!U13</f>
+        <v>48.174999999999997</v>
+      </c>
+      <c r="F22">
+        <f>'3.4.2'!U13</f>
+        <v>311.14166666666699</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="26"/>
+        <v>-0.68333333333301027</v>
+      </c>
+    </row>
+    <row r="23" ht="15">
       <c r="B23" s="4" t="str">
-        <f aca="false">B11</f>
+        <f t="shared" si="27"/>
         <v>Blaugrün</v>
       </c>
-      <c r="D23" s="0" t="n">
-        <f aca="false">'3.4.1'!U14</f>
-        <v>48.3166666666666</v>
-      </c>
-      <c r="F23" s="0" t="n">
-        <f aca="false">'3.4.2'!U14</f>
+      <c r="D23">
+        <f>'3.4.1'!U14</f>
+        <v>48.316666666666599</v>
+      </c>
+      <c r="F23">
+        <f>'3.4.2'!U14</f>
         <v>311</v>
       </c>
-      <c r="I23" s="0" t="n">
-        <f aca="false">D23-(360-F23)</f>
-        <v>-0.683333333333358</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23">
+        <f t="shared" si="26"/>
+        <v>-0.68333333333340107</v>
+      </c>
+    </row>
+    <row r="24" ht="15">
       <c r="B24" s="4" t="str">
-        <f aca="false">B12</f>
+        <f t="shared" si="27"/>
         <v>Blau</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <f aca="false">'3.4.1'!U15</f>
-        <v>48.6333333333333</v>
-      </c>
-      <c r="F24" s="0" t="n">
-        <f aca="false">'3.4.2'!U15</f>
-        <v>310.641666666667</v>
-      </c>
-      <c r="I24" s="0" t="n">
-        <f aca="false">D24-(360-F24)</f>
-        <v>-0.72499999999998</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24">
+        <f>'3.4.1'!U15</f>
+        <v>48.633333333333297</v>
+      </c>
+      <c r="F24">
+        <f>'3.4.2'!U15</f>
+        <v>310.64166666666699</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="26"/>
+        <v>-0.7249999999997101</v>
+      </c>
+    </row>
+    <row r="25" ht="15">
       <c r="B25" s="4" t="str">
-        <f aca="false">B13</f>
+        <f t="shared" si="27"/>
         <v>Violett</v>
       </c>
-      <c r="D25" s="0" t="n">
-        <f aca="false">'3.4.1'!U16</f>
+      <c r="D25">
+        <f>'3.4.1'!U16</f>
         <v>49.125</v>
       </c>
-      <c r="F25" s="0" t="n">
-        <f aca="false">'3.4.2'!U16</f>
-        <v>310.141666666667</v>
-      </c>
-      <c r="I25" s="0" t="n">
-        <f aca="false">D25-(360-F25)</f>
-        <v>-0.733333333333313</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25">
+        <f>'3.4.2'!U16</f>
+        <v>310.14166666666699</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="26"/>
+        <v>-0.73333333333300743</v>
+      </c>
+    </row>
+    <row r="26" ht="15">
       <c r="B26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15">
       <c r="B27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15">
       <c r="B28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15">
       <c r="B29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15">
       <c r="B30" s="4"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70069444444444484" right="0.70069444444444484" top="0.75208333333333299" bottom="0.75208333333333299" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4">
+        <v>706.53999999999996</v>
+      </c>
+      <c r="C4">
+        <v>46.533333333333303</v>
+      </c>
+      <c r="D4" s="5">
+        <f>SIN(RADIANS((C4+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.3933068033937048</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5">
+        <v>667.82000000000005</v>
+      </c>
+      <c r="C5">
+        <v>46.700000000000003</v>
+      </c>
+      <c r="D5" s="5">
+        <f>SIN(RADIANS((C5+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.3977178201951883</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6">
+        <v>587.55999999999995</v>
+      </c>
+      <c r="C6">
+        <v>47.25</v>
+      </c>
+      <c r="D6" s="5">
+        <f>SIN(RADIANS((C6+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.4122381382102893</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7">
+        <v>501.56999999999999</v>
+      </c>
+      <c r="C7">
+        <v>48.174999999999997</v>
+      </c>
+      <c r="D7" s="5">
+        <f>SIN(RADIANS((C7+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.4365331829467354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8">
+        <v>492.19</v>
+      </c>
+      <c r="C8">
+        <v>48.316666666666599</v>
+      </c>
+      <c r="D8" s="5">
+        <f>SIN(RADIANS((C8+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.4402400655214738</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9">
+        <v>447.14999999999998</v>
+      </c>
+      <c r="C9">
+        <v>48.633333333333297</v>
+      </c>
+      <c r="D9" s="5">
+        <f>SIN(RADIANS((C9+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.4485125439748496</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10">
+        <v>438.79000000000002</v>
+      </c>
+      <c r="C10">
+        <v>49.125</v>
+      </c>
+      <c r="D10" s="5">
+        <f>SIN(RADIANS((C10+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+        <v>2.4613195788436246</v>
+      </c>
+    </row>
+    <row r="14" ht="15">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="15">
+      <c r="B16">
+        <f>'3.3'!C22</f>
+        <v>-29.991666666666504</v>
+      </c>
+    </row>
+    <row r="17" ht="15">
+      <c r="B17">
+        <f>ABS(B16)</f>
+        <v>29.991666666666504</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
+++ b/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="3.1" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">Versuch 3.1</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t xml:space="preserve">Geschätzte Abweichung:  (')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abweichung in °</t>
   </si>
   <si>
     <t xml:space="preserve">Prisemnwinkel γ</t>
@@ -2717,6 +2720,15 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" ht="14.25">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <f>E11/60</f>
+        <v>0.016666666666666666</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.70069444444444484" right="0.70069444444444484" top="0.75208333333333299" bottom="0.75208333333333299" header="0.51181102362204689" footer="0.51181102362204689"/>
@@ -2735,10 +2747,10 @@
   <sheetData>
     <row r="4" ht="14.25">
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4">
         <f>'3.1'!O7</f>
@@ -2747,16 +2759,16 @@
     </row>
     <row r="6" ht="14.25">
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -2775,18 +2787,18 @@
     </row>
     <row r="12" ht="14.25">
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <f>C8+(D8/60)</f>
@@ -2806,7 +2818,7 @@
     </row>
     <row r="16" ht="14.25">
       <c r="C16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <f>F8+(G8/60)</f>
@@ -2823,7 +2835,7 @@
     </row>
     <row r="19" ht="14.25">
       <c r="C19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="14.25">
@@ -2853,10 +2865,10 @@
   <sheetData>
     <row r="3" ht="14.25">
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <f>'3.1'!E11</f>
@@ -2865,62 +2877,62 @@
     </row>
     <row r="4" ht="14.25">
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <f>'3.1'!O7</f>
         <v>-0.47500000000002301</v>
       </c>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10">
         <v>706.53999999999996</v>
@@ -2962,7 +2974,7 @@
     </row>
     <row r="11" ht="14.25">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>667.82000000000005</v>
@@ -3004,7 +3016,7 @@
     </row>
     <row r="12" ht="14.25">
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12">
         <v>587.55999999999995</v>
@@ -3046,7 +3058,7 @@
     </row>
     <row r="13" ht="14.25">
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13">
         <v>501.56999999999999</v>
@@ -3088,7 +3100,7 @@
     </row>
     <row r="14" ht="14.25">
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>492.19</v>
@@ -3130,7 +3142,7 @@
     </row>
     <row r="15" ht="14.25">
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15">
         <v>447.14999999999998</v>
@@ -3172,7 +3184,7 @@
     </row>
     <row r="16" ht="14.25">
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16">
         <v>438.79000000000002</v>
@@ -3214,40 +3226,40 @@
     </row>
     <row r="17" ht="14.25">
       <c r="O17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="14.25">
@@ -3494,11 +3506,11 @@
   <sheetData>
     <row r="3" ht="14.25">
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4">
         <f>'3.1'!E11</f>
@@ -3527,7 +3539,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4">
         <f>'3.1'!O7</f>
@@ -3545,7 +3557,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -3580,7 +3592,7 @@
     </row>
     <row r="6" ht="14.25">
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3597,7 +3609,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -3632,46 +3644,46 @@
     </row>
     <row r="8" ht="14.25">
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -4093,7 +4105,7 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -4130,7 +4142,7 @@
     </row>
     <row r="19" ht="14.25">
       <c r="B19" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -4180,30 +4192,30 @@
     </row>
     <row r="21" ht="14.25">
       <c r="B21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -4963,16 +4975,16 @@
   <sheetData>
     <row r="4" ht="15">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" ht="15">
@@ -5103,16 +5115,16 @@
     </row>
     <row r="17" ht="15">
       <c r="D17" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" ht="15">
@@ -5274,13 +5286,13 @@
   <sheetData>
     <row r="3">
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -5369,7 +5381,7 @@
     </row>
     <row r="14" ht="15">
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="15">

--- a/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
+++ b/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="3.1" sheetId="1" state="visible" r:id="rId1"/>
@@ -261,7 +261,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -275,9 +275,6 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -2784,6 +2781,10 @@
       <c r="G8">
         <v>3</v>
       </c>
+      <c r="L8">
+        <f>1/60</f>
+        <v>0.016666666666666666</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
       <c r="D12" t="s">
@@ -2842,6 +2843,10 @@
       <c r="C22" s="3">
         <f>(D14-D16)/2</f>
         <v>-29.991666666666504</v>
+      </c>
+      <c r="D22">
+        <f>C22*2</f>
+        <v>-59.983333333333007</v>
       </c>
     </row>
   </sheetData>
@@ -5302,8 +5307,8 @@
       <c r="C4">
         <v>46.533333333333303</v>
       </c>
-      <c r="D4" s="5">
-        <f>SIN(RADIANS((C4+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+      <c r="D4" s="3">
+        <f t="shared" ref="D4:D9" si="28">SIN(RADIANS((C4+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
         <v>2.3933068033937048</v>
       </c>
     </row>
@@ -5314,8 +5319,8 @@
       <c r="C5">
         <v>46.700000000000003</v>
       </c>
-      <c r="D5" s="5">
-        <f>SIN(RADIANS((C5+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+      <c r="D5" s="3">
+        <f t="shared" si="28"/>
         <v>2.3977178201951883</v>
       </c>
     </row>
@@ -5326,8 +5331,8 @@
       <c r="C6">
         <v>47.25</v>
       </c>
-      <c r="D6" s="5">
-        <f>SIN(RADIANS((C6+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+      <c r="D6" s="3">
+        <f t="shared" si="28"/>
         <v>2.4122381382102893</v>
       </c>
     </row>
@@ -5338,8 +5343,8 @@
       <c r="C7">
         <v>48.174999999999997</v>
       </c>
-      <c r="D7" s="5">
-        <f>SIN(RADIANS((C7+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+      <c r="D7" s="3">
+        <f t="shared" si="28"/>
         <v>2.4365331829467354</v>
       </c>
     </row>
@@ -5350,8 +5355,8 @@
       <c r="C8">
         <v>48.316666666666599</v>
       </c>
-      <c r="D8" s="5">
-        <f>SIN(RADIANS((C8+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+      <c r="D8" s="3">
+        <f t="shared" si="28"/>
         <v>2.4402400655214738</v>
       </c>
     </row>
@@ -5362,8 +5367,8 @@
       <c r="C9">
         <v>48.633333333333297</v>
       </c>
-      <c r="D9" s="5">
-        <f>SIN(RADIANS((C9+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
+      <c r="D9" s="3">
+        <f t="shared" si="28"/>
         <v>2.4485125439748496</v>
       </c>
     </row>
@@ -5374,7 +5379,7 @@
       <c r="C10">
         <v>49.125</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <f>SIN(RADIANS((C10+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
         <v>2.4613195788436246</v>
       </c>

--- a/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
+++ b/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="3.1" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve">Versuch 3.1</t>
   </si>
@@ -218,12 +218,51 @@
   <si>
     <t>n</t>
   </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>A_glass</t>
+  </si>
+  <si>
+    <t>B_glass</t>
+  </si>
+  <si>
+    <t>Abweichung</t>
+  </si>
+  <si>
+    <t>Quarzglas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borsilikatglas (BK7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kronglas (K5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barium-Kronglas (BaK4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flintglas (F2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barium-Flintglas (BaF10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dichtes Flintglas (SF10)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -232,6 +271,11 @@
     <font>
       <sz val="10.000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="64"/>
+      <name val="Liberation Serif"/>
     </font>
   </fonts>
   <fills count="2">
@@ -261,7 +305,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -275,6 +319,17 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" indent="3"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" indent="3"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -5287,7 +5342,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3">
       <c r="B3" t="s">
@@ -5311,6 +5366,12 @@
         <f t="shared" ref="D4:D9" si="28">SIN(RADIANS((C4+$B$17)/2))/SIN((RADIANS($B$17/2)))</f>
         <v>2.3933068033937048</v>
       </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8640.2000000000007</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5">
@@ -5334,6 +5395,12 @@
       <c r="D6" s="3">
         <f t="shared" si="28"/>
         <v>2.4122381382102893</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="6">
+        <v>2353230</v>
       </c>
     </row>
     <row r="7">
@@ -5400,6 +5467,137 @@
         <f>ABS(B16)</f>
         <v>29.991666666666504</v>
       </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20">
+        <v>1.458</v>
+      </c>
+      <c r="G20">
+        <v>0.0035400000000000002</v>
+      </c>
+      <c r="I20">
+        <f>(($G$4/1000)-G20)/(G20*100)</f>
+        <v>24.397344632768363</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21">
+        <v>1.5045999999999999</v>
+      </c>
+      <c r="G21">
+        <v>0.0041999999999999997</v>
+      </c>
+      <c r="I21">
+        <f>(($G$4/1000)-G21)/(G21*100)</f>
+        <v>20.56190476190476</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22">
+        <v>1.522</v>
+      </c>
+      <c r="G22">
+        <v>0.0045900000000000003</v>
+      </c>
+      <c r="I22">
+        <f>(($G$4/1000)-G22)/(G22*100)</f>
+        <v>18.813965141612201</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23">
+        <v>1.569</v>
+      </c>
+      <c r="G23">
+        <v>0.0053099999999999996</v>
+      </c>
+      <c r="I23">
+        <f>(($G$4/1000)-G23)/(G23*100)</f>
+        <v>16.261563088512244</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="7">
+        <v>15904</v>
+      </c>
+      <c r="G24">
+        <v>0.0057099999999999998</v>
+      </c>
+      <c r="I24">
+        <f>(($G$4/1000)-G24)/(G24*100)</f>
+        <v>15.121698774080562</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25">
+        <v>1.6699999999999999</v>
+      </c>
+      <c r="G25">
+        <v>0.00743</v>
+      </c>
+      <c r="I25">
+        <f>(($G$4/1000)-G25)/(G25*100)</f>
+        <v>11.618802153432034</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26">
+        <v>1.728</v>
+      </c>
+      <c r="G26">
+        <v>0.01342</v>
+      </c>
+      <c r="I26">
+        <f>(($G$4/1000)-G26)/(G26*100)</f>
+        <v>6.4283010432190766</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="E27"/>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="E30"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="E33"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="E36"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
+++ b/Prinsmenspektrometer/Messungenen Digitalisiert.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t xml:space="preserve">Versuch 3.1</t>
   </si>
@@ -257,12 +257,24 @@
   <si>
     <t xml:space="preserve">dichtes Flintglas (SF10)</t>
   </si>
+  <si>
+    <t xml:space="preserve">λ (nm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">δmin (°)</t>
+  </si>
+  <si>
+    <t>u(n)</t>
+  </si>
+  <si>
+    <t>u(n)/n</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -274,8 +286,12 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Liberation Serif"/>
+    </font>
+    <font>
+      <sz val="10.500000"/>
+      <color rgb="FF171717"/>
+      <name val="Liberation Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -305,7 +321,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -330,6 +346,13 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -5370,7 +5393,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="5">
-        <v>8640.2000000000007</v>
+        <v>0.0086402000000000007</v>
       </c>
     </row>
     <row r="5">
@@ -5482,6 +5505,9 @@
         <v>65</v>
       </c>
     </row>
+    <row r="19" ht="14.25">
+      <c r="O19"/>
+    </row>
     <row r="20" ht="14.25">
       <c r="C20" t="s">
         <v>66</v>
@@ -5493,9 +5519,10 @@
         <v>0.0035400000000000002</v>
       </c>
       <c r="I20">
-        <f>(($G$4/1000)-G20)/(G20*100)</f>
-        <v>24.397344632768363</v>
-      </c>
+        <f>100*ABS($G$4-G20)/G20</f>
+        <v>144.07344632768365</v>
+      </c>
+      <c r="O20"/>
     </row>
     <row r="21" ht="14.25">
       <c r="C21" t="s">
@@ -5508,9 +5535,10 @@
         <v>0.0041999999999999997</v>
       </c>
       <c r="I21">
-        <f>(($G$4/1000)-G21)/(G21*100)</f>
-        <v>20.56190476190476</v>
-      </c>
+        <f>100*ABS($G$4-G21)/G21</f>
+        <v>105.71904761904764</v>
+      </c>
+      <c r="O21"/>
     </row>
     <row r="22" ht="14.25">
       <c r="C22" t="s">
@@ -5523,9 +5551,10 @@
         <v>0.0045900000000000003</v>
       </c>
       <c r="I22">
-        <f>(($G$4/1000)-G22)/(G22*100)</f>
-        <v>18.813965141612201</v>
-      </c>
+        <f>100*ABS($G$4-G22)/G22</f>
+        <v>88.239651416122001</v>
+      </c>
+      <c r="O22"/>
     </row>
     <row r="23" ht="14.25">
       <c r="C23" t="s">
@@ -5538,9 +5567,10 @@
         <v>0.0053099999999999996</v>
       </c>
       <c r="I23">
-        <f>(($G$4/1000)-G23)/(G23*100)</f>
-        <v>16.261563088512244</v>
-      </c>
+        <f>100*ABS($G$4-G23)/G23</f>
+        <v>62.71563088512243</v>
+      </c>
+      <c r="O23"/>
     </row>
     <row r="24" ht="14.25">
       <c r="C24" t="s">
@@ -5553,9 +5583,10 @@
         <v>0.0057099999999999998</v>
       </c>
       <c r="I24">
-        <f>(($G$4/1000)-G24)/(G24*100)</f>
-        <v>15.121698774080562</v>
-      </c>
+        <f>100*ABS($G$4-G24)/G24</f>
+        <v>51.316987740805615</v>
+      </c>
+      <c r="O24"/>
     </row>
     <row r="25" ht="14.25">
       <c r="C25" t="s">
@@ -5568,9 +5599,10 @@
         <v>0.00743</v>
       </c>
       <c r="I25">
-        <f>(($G$4/1000)-G25)/(G25*100)</f>
-        <v>11.618802153432034</v>
-      </c>
+        <f>100*ABS($G$4-G25)/G25</f>
+        <v>16.288021534320333</v>
+      </c>
+      <c r="O25"/>
     </row>
     <row r="26" ht="14.25">
       <c r="C26" t="s">
@@ -5583,21 +5615,312 @@
         <v>0.01342</v>
       </c>
       <c r="I26">
-        <f>(($G$4/1000)-G26)/(G26*100)</f>
-        <v>6.4283010432190766</v>
-      </c>
+        <f>100*ABS($G$4-G26)/G26</f>
+        <v>35.616989567809235</v>
+      </c>
+      <c r="O26"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="E27"/>
+      <c r="O27"/>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="K28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" ht="25.5">
+      <c r="K29" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L29" s="8">
+        <v>706.53999999999996</v>
+      </c>
+      <c r="M29" s="8">
+        <v>46.854199999999999</v>
+      </c>
+      <c r="N29" s="8">
+        <v>2.4018000000000002</v>
+      </c>
+      <c r="O29" s="8">
+        <v>0.0027529999999999998</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0.0011459999999999999</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
-      <c r="E30"/>
+      <c r="K30" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L30" s="8">
+        <v>667.82000000000005</v>
+      </c>
+      <c r="M30" s="8">
+        <v>47.037500000000001</v>
+      </c>
+      <c r="N30" s="8">
+        <v>2.4066000000000001</v>
+      </c>
+      <c r="O30" s="8">
+        <v>0.0027569999999999999</v>
+      </c>
+      <c r="P30" s="8">
+        <v>0.0011459999999999999</v>
+      </c>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="9"/>
+      <c r="T30"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="K31" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L31" s="8">
+        <v>587.55999999999995</v>
+      </c>
+      <c r="M31" s="8">
+        <v>47.587499999999999</v>
+      </c>
+      <c r="N31" s="8">
+        <v>2.4211</v>
+      </c>
+      <c r="O31" s="8">
+        <v>0.002771</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0.001145</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="K32" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L32" s="8">
+        <v>501.56999999999999</v>
+      </c>
+      <c r="M32" s="8">
+        <v>48.5167</v>
+      </c>
+      <c r="N32" s="8">
+        <v>2.4455</v>
+      </c>
+      <c r="O32" s="8">
+        <v>0.0027950000000000002</v>
+      </c>
+      <c r="P32" s="8">
+        <v>0.0011429999999999999</v>
+      </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="E33"/>
+      <c r="K33" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="8">
+        <v>492.19</v>
+      </c>
+      <c r="M33" s="8">
+        <v>48.658299999999997</v>
+      </c>
+      <c r="N33" s="8">
+        <v>2.4491999999999998</v>
+      </c>
+      <c r="O33" s="8">
+        <v>0.0027980000000000001</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0.0011429999999999999</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="K34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L34" s="8">
+        <v>447.14999999999998</v>
+      </c>
+      <c r="M34" s="8">
+        <v>48.995800000000003</v>
+      </c>
+      <c r="N34" s="8">
+        <v>2.4580000000000002</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0.002807</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0.001142</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="K35" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L35" s="8">
+        <v>438.79000000000002</v>
+      </c>
+      <c r="M35" s="8">
+        <v>49.491700000000002</v>
+      </c>
+      <c r="N35" s="8">
+        <v>2.4708000000000001</v>
+      </c>
+      <c r="O35" s="8">
+        <v>0.0028189999999999999</v>
+      </c>
+      <c r="P35" s="8">
+        <v>0.0011409999999999999</v>
+      </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="E36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="O37"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="O38"/>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="O39"/>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="O40"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="O41"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="O42"/>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="O43"/>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="O44"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="O45"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="O46"/>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="O47"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="O48"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="O49"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="O50"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="O51"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="O52"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="O53"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="O54"/>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="O55"/>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="O56"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="O57"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="O58"/>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="O59"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="O60"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="O61"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="O62"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="O63"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="O64"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="O65"/>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="O66"/>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="O67"/>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="O68"/>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="O69"/>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="O70"/>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="O71"/>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="O72"/>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="O73"/>
+    </row>
+    <row r="74" ht="14.25">
+      <c r="O74"/>
+    </row>
+    <row r="75" ht="14.25">
+      <c r="O75"/>
+    </row>
+    <row r="76" ht="14.25">
+      <c r="O76"/>
+    </row>
+    <row r="77" ht="14.25">
+      <c r="O77"/>
+    </row>
+    <row r="78" ht="14.25">
+      <c r="O78"/>
+    </row>
+    <row r="79" ht="14.25">
+      <c r="O79"/>
+    </row>
+    <row r="80" ht="14.25">
+      <c r="O80"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
